--- a/reports/Daily Check.xlsx
+++ b/reports/Daily Check.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\EST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamza\Desktop\EST-IMS Online\est-ims\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369C7F98-F34C-4465-8A9B-E46A40BF1997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E346D190-C8A2-460C-B8CC-78CE79BE037D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <t>Daily Check</t>
   </si>
   <si>
-    <t>Data: 16/05/2026</t>
+    <t>Data: 23/05/2026</t>
   </si>
 </sst>
 </file>
@@ -196,6 +196,56 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2997926</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600282</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>431021</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAA4EC45-9B98-4518-A9FE-93D038E03EB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6331676" y="3524250"/>
+          <a:ext cx="4365106" cy="2564621"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -729,7 +779,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="93" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;CEST Inventory Management System
 </oddHeader>
